--- a/fhir/finnish-smart/StructureDefinition-fi-smart-allergy-intolerance.xlsx
+++ b/fhir/finnish-smart/StructureDefinition-fi-smart-allergy-intolerance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-rc2</t>
+    <t>2.0.0-rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-11T17:07:13+03:00</t>
+    <t>2025-06-01T15:36:45+03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/finnish-smart/StructureDefinition-fi-smart-allergy-intolerance.xlsx
+++ b/fhir/finnish-smart/StructureDefinition-fi-smart-allergy-intolerance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-rc3</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-01T15:36:45+03:00</t>
+    <t>2025-10-26T13:24:16+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -362,7 +362,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -661,7 +661,7 @@
     <t>Type of the substance/product, allergy or intolerance condition, or negation/exclusion codes for reporting no known allergies.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/allergyintolerance-code</t>
+    <t>http://hl7.org/fhir/ValueSet/allergyintolerance-code|4.0.1</t>
   </si>
   <si>
     <t>substance/product:@@ -690,7 +690,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(Patient|4.0.1)
 </t>
   </si>
   <si>
@@ -712,7 +712,7 @@
     <t>AllergyIntolerance.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -776,7 +776,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -799,7 +799,7 @@
 Informant</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson|Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -931,7 +931,7 @@
     <t>Codes defining the type of the substance (including pharmaceutical products).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/substance-code</t>
+    <t>http://hl7.org/fhir/ValueSet/substance-code|4.0.1</t>
   </si>
   <si>
     <t>outBoundRelationship[typeCode=SAS].target[classCode=SBADM, code &lt;= ExposureCode].participation[typeCode=CSM].role[classCode=ADMM].player[classCode=MAT, determinerCode=KIND, code &lt;= ExposureAgentEntityType]</t>
@@ -956,7 +956,7 @@
     <t>Clinical symptoms and/or signs that are observed or associated with an Adverse Reaction Event.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>AL1-5</t>
@@ -1026,7 +1026,7 @@
     <t>A coded concept describing the route or physiological path of administration of a therapeutic agent into or onto the body of a subject.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
   </si>
   <si>
     <t>outBoundRelationship[typeCode=SAS].target[classCode=SBADM, code &lt;= ExposureCode].routeCode</t>
@@ -1356,7 +1356,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="48.2109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="66.578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
